--- a/02_加值成品/九上/九上3-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上3-1_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上3-1 功與功率　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國三上學期 九上3-1 功與功率　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>功的公式是？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>W=F×s</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>做功越快</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>不做功</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>力乘位移</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>功的單位是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>焦耳/秒</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>功率</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>焦耳(J)</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>不做功</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>能量單位</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>功率的公式是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>P=W/t</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>不做功</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>焦耳(J)</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>功除時間</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>功率的單位是？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>瓦特(W)</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>功率</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
           <t>快慢</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="34" customHeight="1">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>焦耳/秒</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>快慢</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>力與位移垂直做功嗎？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>W=F×s</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>不做功</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>焦耳(J)</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>垂直</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>沒有位移有做功嗎？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>沒有</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>P=W/t</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>瓦特(W)</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>快慢</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>無位移</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>功率表示做功的？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>快慢</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>焦耳(J)</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>做功越快</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>效率</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>提重物原地不動做功嗎？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>P=W/t</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>功率</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>快慢</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>不做</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>無位移</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>做功需要力與什麼？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>否,重力垂直位移</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>沿力方向的位移</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>功相同,甲功率大</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>沿位移方向的分量</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>做功</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>功率單位瓦特等於？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>相同</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>功率</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>焦耳/秒</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>瓦特(W)</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>J/s</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上3-1 功與功率　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國三上學期 九上3-1 功與功率　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>力10N移動3m,功？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>50 J</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>30 J</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>500 J</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>100 J</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>F×s</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>做功60J花3秒,功率？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>20 W</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>20J;4W</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>50 J</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>500 J</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>W/t</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>功率50W做功10秒,功？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>30 J</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>500 J</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>50 J</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>100 J</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>P×t</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>水平提重物走路對重物做功？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>沿力方向的位移</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>重力方向垂直於水平位移</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>否,重力垂直位移</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>不做(力垂直位移)</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>垂直</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>力20N位移5m,功？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>500 J</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>100 J</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>30 J</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>50 J</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>F×s</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>同樣搬到三樓,快慢影響功嗎？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>沿力方向的位移</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>功相同,甲功率大</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>功=重力×高度</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>不影響功,影響功率</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>區別</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>功率越大代表？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>做功越快</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>功率</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>相同</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>焦耳(J)</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>快慢</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>做功100J用5秒功率？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>30 J</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>20J;4W</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>100 J</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>20 W</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>W/t</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>力25N移動2m做功？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>100 J</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>30 J</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>500 J</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>50 J</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>F×s</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>做功200J花10秒功率？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>100W</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>60J;6W</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>20 W</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>500 J</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>W/t</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上3-1 功與功率　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國三上學期 九上3-1 功與功率　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>甲乙搬同重物上同樓,甲較快誰功率大功呢？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>功相同,甲功率大</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>功=重力×高度</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>沿位移方向的分量</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>不做(力垂直位移)</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>功vs功率</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>為何水平提重物走路不做功？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>沿力方向的位移</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>不影響功,影響功率</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>重力方向垂直於水平位移</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>不做(力垂直位移)</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>垂直不做功</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>力15N拉物移動4m,功?若10秒完成功率？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>30 J</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>20J;4W</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>60J;6W</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>100 J</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>綜合</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>爬樓梯對抗重力做功與體重樓高關係？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>功=重力×高度</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>沿位移方向的分量</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>重力方向垂直於水平位移</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>不做(力垂直位移)</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>重力功</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>功率100W與60W燈泡誰耗能快？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>30 J</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>100W</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>20J;4W</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>20 W</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>功率</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>搬磚上樓分兩次與一次總功相同嗎？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>焦耳/秒</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>焦耳(J)</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>相同</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>不做功</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>守恆</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>力與位移成角度時只有哪個分量做功？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>重力方向垂直於水平位移</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>沿力方向的位移</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>功相同,甲功率大</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>沿位移方向的分量</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>分量</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>馬力是什麼量的單位？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>功率</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>瓦特(W)</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>焦耳(J)</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>做功越快</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>引擎</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>把10N重物舉高2m做功?若5秒完成功率?</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>100 J</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>500 J</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>20J;4W</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>100W</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>綜合</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>沿水平搬重物走路對重物是否做功?為何</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>否,重力垂直位移</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>沿位移方向的分量</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>功=重力×高度</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>不做(力垂直位移)</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>垂直</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/九上/九上3-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上3-1_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>力乘位移</t>
+          <t>力乘位移：功等於施的力乘以物體沿著力的方向移動的距離</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>能量單位</t>
+          <t>能量單位：功和能量是同一種東西,單位都用焦耳來表示</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>功除時間</t>
+          <t>功除時間：功率等於做的功除以花掉的時間,代表做功有多快</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>快慢</t>
+          <t>快慢：瓦特是功率的單位,數字越大代表做功的速度越快</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>垂直</t>
+          <t>垂直：如果施力方向和物體移動方向互相垂直,這個力完全沒有做功</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>無位移</t>
+          <t>無位移：不管出多大的力,只要物體完全沒有移動,就沒有做功</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>效率</t>
+          <t>效率：功率就是在講做同樣的功時,是花比較多時間還是比較少時間完成</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>無位移</t>
+          <t>無位移：手雖然出力撐住重物,但重物沒有移動位置,所以沒有做功</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>做功</t>
+          <t>做功：物理上「做功」的條件是要有力,而且物體要沿著這個力的方向產生位移,兩者缺一不可</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>J/s</t>
+          <t>J/s：功率是做功的快慢,單位瓦特(W)定義為每秒做1焦耳的功,也就是J/s</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>F×s</t>
+          <t>F×s：力10牛頓乘以移動距離3公尺,等於做功30焦耳</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>W/t</t>
+          <t>W/t：做的功60焦耳除以花費時間3秒,等於功率20瓦特</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>P×t</t>
+          <t>P×t：功率50瓦特乘以時間10秒,等於總共做了500焦耳的功</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>垂直</t>
+          <t>垂直：手往上撐重物的力是垂直方向,但人是水平前進,力和位移垂直所以不做功</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>F×s</t>
+          <t>F×s：力20牛頓乘以位移5公尺,等於做功100焦耳</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>區別</t>
+          <t>區別：搬到同樣高度做的功是固定的,但花的時間不同會讓功率不一樣</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>快慢</t>
+          <t>快慢：功率的數值越大,代表在同樣時間內能完成更多的功</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>W/t</t>
+          <t>W/t：做的功100焦耳除以時間5秒,等於功率20瓦特</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>F×s</t>
+          <t>F×s：做功=力×沿力方向的位移,25牛頓乘以2公尺等於50焦耳</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>W/t</t>
+          <t>W/t：功率=做的功÷所花時間,200焦耳除以10秒等於20瓦特</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>功vs功率</t>
+          <t>功vs功率：兩人做的功一樣多因為高度重量相同,但甲花的時間較少所以甲的功率比較大</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>垂直不做功</t>
+          <t>垂直不做功：手施的力是為了對抗垂直向下的重力,但走路的位移是水平方向,兩者垂直所以不算做功</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>綜合</t>
+          <t>綜合：先算功,力15乘距離4等於60焦耳;再算功率,60焦耳除以10秒等於6瓦特</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>重力功</t>
+          <t>重力功：對抗重力往上爬所做的功,等於體重(重力)乘以爬升的高度</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>功率</t>
+          <t>功率：功率數字越大代表單位時間消耗的能量越多,所以100瓦的燈泡耗能較快</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>守恆</t>
+          <t>守恆：不管分幾次搬,只要總重量和總爬升高度一樣,做的總功就會相同</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>分量</t>
+          <t>分量：斜著出力時,只有和移動方向同方向的那一部分力才真正對物體做功</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>引擎</t>
+          <t>引擎：馬力和瓦特一樣,都是用來表示引擎做功快慢的功率單位</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>綜合</t>
+          <t>綜合：做功=力×位移=10×2=20焦耳;功率=功÷時間=20÷5=4瓦特</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>垂直</t>
+          <t>垂直：手施的力是向上撐住重物,但重物移動的方向是水平的,力的方向與位移方向垂直,所以這個力沒有對重物做功</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/九上/九上3-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上3-1_三種難度測驗卷.xlsx
@@ -723,22 +723,22 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
+          <t>相同</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>功率</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>不做功</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
           <t>W=F×s</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>沒有</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>不做功</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>焦耳(J)</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -843,17 +843,17 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>P=W/t</t>
+          <t>功率</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>功率</t>
+          <t>相同</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>快慢</t>
+          <t>沒有</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
